--- a/data/MACHINES PRICES.xlsx
+++ b/data/MACHINES PRICES.xlsx
@@ -1,20 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pavan\projects\Quot-proj\smartquotation-app\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2775F6FA-1B09-4281-89EC-117A727406BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="105" windowWidth="14295" windowHeight="4635"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="49">
   <si>
     <t>S.L.NO</t>
   </si>
@@ -155,17 +172,23 @@
   </si>
   <si>
     <t xml:space="preserve">VACUUM CLEANERS </t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Price</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -262,23 +285,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -286,11 +301,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -299,13 +310,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -343,7 +362,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -377,6 +396,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -411,9 +431,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -586,17 +607,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="C6:J84"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="44.140625" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="31.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" customWidth="1"/>
+    <col min="4" max="4" width="44.109375" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="9" max="9" width="31.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="3:10" ht="15.75">
+    <row r="6" spans="3:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C6" s="1" t="s">
         <v>0</v>
       </c>
@@ -616,7 +637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="3:10">
+    <row r="7" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C7" s="3">
         <v>1</v>
       </c>
@@ -636,7 +657,7 @@
         <v>3895</v>
       </c>
     </row>
-    <row r="8" spans="3:10">
+    <row r="8" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C8" s="3">
         <v>2</v>
       </c>
@@ -656,7 +677,7 @@
         <v>9735</v>
       </c>
     </row>
-    <row r="9" spans="3:10">
+    <row r="9" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C9" s="3">
         <v>3</v>
       </c>
@@ -676,7 +697,7 @@
         <v>3365</v>
       </c>
     </row>
-    <row r="10" spans="3:10">
+    <row r="10" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C10" s="3">
         <v>4</v>
       </c>
@@ -696,7 +717,7 @@
         <v>10525</v>
       </c>
     </row>
-    <row r="11" spans="3:10">
+    <row r="11" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C11" s="3">
         <v>5</v>
       </c>
@@ -706,17 +727,17 @@
       <c r="E11" s="5">
         <v>10212</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="3">
         <v>5</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="12">
+      <c r="J11" s="9">
         <v>9125</v>
       </c>
     </row>
-    <row r="12" spans="3:10">
+    <row r="12" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C12" s="3">
         <v>6</v>
       </c>
@@ -726,17 +747,17 @@
       <c r="E12" s="5">
         <v>51236</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="3">
         <v>6</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="9">
         <v>12922</v>
       </c>
     </row>
-    <row r="13" spans="3:10">
+    <row r="13" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C13" s="3">
         <v>7</v>
       </c>
@@ -746,17 +767,17 @@
       <c r="E13" s="5">
         <v>800491</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="3">
         <v>7</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="9">
         <v>10878</v>
       </c>
     </row>
-    <row r="14" spans="3:10">
+    <row r="14" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C14" s="3">
         <v>8</v>
       </c>
@@ -766,17 +787,17 @@
       <c r="E14" s="7">
         <v>85909</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="3">
         <v>8</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="9">
         <v>7367</v>
       </c>
     </row>
-    <row r="15" spans="3:10">
+    <row r="15" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C15" s="3">
         <v>9</v>
       </c>
@@ -786,13 +807,13 @@
       <c r="E15" s="5">
         <v>61820</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="3">
         <v>9</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
     </row>
-    <row r="16" spans="3:10">
+    <row r="16" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C16" s="3">
         <v>10</v>
       </c>
@@ -802,13 +823,13 @@
       <c r="E16" s="5">
         <v>178457</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="3">
         <v>10</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
     </row>
-    <row r="17" spans="3:10">
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C17" s="3">
         <v>11</v>
       </c>
@@ -818,13 +839,13 @@
       <c r="E17" s="5">
         <v>273321</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="3">
         <v>11</v>
       </c>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
     </row>
-    <row r="18" spans="3:10">
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C18" s="3">
         <v>12</v>
       </c>
@@ -834,13 +855,13 @@
       <c r="E18" s="5">
         <v>95118</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="3">
         <v>12</v>
       </c>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
     </row>
-    <row r="19" spans="3:10">
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C19" s="3">
         <v>13</v>
       </c>
@@ -850,13 +871,13 @@
       <c r="E19" s="5">
         <v>107552</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="3">
         <v>13</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
     </row>
-    <row r="20" spans="3:10">
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C20" s="3">
         <v>14</v>
       </c>
@@ -866,13 +887,13 @@
       <c r="E20" s="5">
         <v>145794</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="3">
         <v>14</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
     </row>
-    <row r="21" spans="3:10">
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C21" s="3">
         <v>15</v>
       </c>
@@ -882,14 +903,14 @@
       <c r="E21" s="5">
         <v>116407</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="3">
         <v>15</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
     </row>
-    <row r="22" spans="3:10">
-      <c r="C22" s="9">
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
         <v>16</v>
       </c>
       <c r="D22" s="4" t="s">
@@ -898,89 +919,89 @@
       <c r="E22" s="5">
         <v>93031</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="3">
         <v>16</v>
       </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
     </row>
-    <row r="23" spans="3:10">
-      <c r="C23" s="9">
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
         <v>17</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="5">
         <v>38036</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="3">
         <v>17</v>
       </c>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
     </row>
-    <row r="24" spans="3:10">
-      <c r="C24" s="9">
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
         <v>18</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="11">
+      <c r="E24" s="5">
         <v>52875</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="3">
         <v>18</v>
       </c>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
     </row>
-    <row r="25" spans="3:10">
-      <c r="C25" s="9">
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
         <v>19</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="11">
+      <c r="E25" s="5">
         <v>61820</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="3">
         <v>19</v>
       </c>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
     </row>
-    <row r="26" spans="3:10">
-      <c r="C26" s="9">
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
         <v>20</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E26" s="11">
+      <c r="E26" s="5">
         <v>77399</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="3">
         <v>20</v>
       </c>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
     </row>
-    <row r="27" spans="3:10">
-      <c r="C27" s="9">
+    <row r="27" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
         <v>21</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E27" s="11">
+      <c r="E27" s="5">
         <v>44232</v>
       </c>
     </row>
-    <row r="28" spans="3:10">
-      <c r="C28" s="9">
+    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C28" s="3">
         <v>22</v>
       </c>
       <c r="D28" s="4" t="s">
@@ -990,19 +1011,19 @@
         <v>567205</v>
       </c>
     </row>
-    <row r="29" spans="3:10">
-      <c r="C29" s="9">
+    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
         <v>23</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E29" s="5">
         <v>815677</v>
       </c>
     </row>
-    <row r="30" spans="3:10">
-      <c r="C30" s="9">
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
         <v>24</v>
       </c>
       <c r="D30" s="4" t="s">
@@ -1012,30 +1033,30 @@
         <v>253247</v>
       </c>
     </row>
-    <row r="31" spans="3:10">
-      <c r="C31" s="9">
+    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
         <v>25</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E31" s="12">
+      <c r="E31" s="9">
         <v>557135</v>
       </c>
     </row>
-    <row r="32" spans="3:10">
-      <c r="C32" s="9">
+    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
         <v>26</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E32" s="12">
+      <c r="E32" s="9">
         <v>800491</v>
       </c>
     </row>
-    <row r="33" spans="3:9">
-      <c r="C33" s="9">
+    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
         <v>27</v>
       </c>
       <c r="D33" s="4" t="s">
@@ -1045,8 +1066,8 @@
         <v>266319</v>
       </c>
     </row>
-    <row r="34" spans="3:9">
-      <c r="C34" s="9">
+    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
         <v>28</v>
       </c>
       <c r="D34" s="4" t="s">
@@ -1056,318 +1077,309 @@
         <v>183871</v>
       </c>
     </row>
-    <row r="35" spans="3:9">
-      <c r="C35" s="9">
+    <row r="35" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C35" s="3">
         <v>29</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E35" s="12">
+      <c r="E35" s="9">
         <v>38036</v>
       </c>
-      <c r="I35" s="13"/>
-    </row>
-    <row r="36" spans="3:9">
-      <c r="C36" s="9"/>
+      <c r="I35" s="10"/>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C36" s="3"/>
       <c r="D36" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E36" s="12">
+      <c r="E36" s="9">
         <v>2152</v>
       </c>
-      <c r="I36" s="13"/>
-    </row>
-    <row r="37" spans="3:9">
-      <c r="C37" s="9">
+      <c r="I36" s="10"/>
+    </row>
+    <row r="37" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C37" s="3">
         <v>30</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E37" s="12">
+      <c r="E37" s="9">
         <v>26057</v>
       </c>
-      <c r="I37" s="13"/>
-    </row>
-    <row r="38" spans="3:9">
-      <c r="C38" s="9">
+      <c r="I37" s="10"/>
+    </row>
+    <row r="38" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C38" s="3">
         <v>31</v>
       </c>
       <c r="D38" t="s">
         <v>44</v>
       </c>
-      <c r="E38" s="16">
+      <c r="E38" s="12">
         <v>173414</v>
       </c>
-      <c r="I38" s="13"/>
-    </row>
-    <row r="39" spans="3:9">
-      <c r="C39" s="9">
+      <c r="I38" s="10"/>
+    </row>
+    <row r="39" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C39" s="3">
         <v>32</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
-      <c r="I39" s="13"/>
-    </row>
-    <row r="40" spans="3:9">
-      <c r="C40" s="9">
+      <c r="I39" s="10"/>
+    </row>
+    <row r="40" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C40" s="3">
         <v>33</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
-      <c r="I40" s="13"/>
-    </row>
-    <row r="41" spans="3:9">
-      <c r="C41" s="9">
+      <c r="I40" s="10"/>
+    </row>
+    <row r="41" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C41" s="3">
         <v>34</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
-      <c r="I41" s="13"/>
-    </row>
-    <row r="42" spans="3:9">
-      <c r="C42" s="9">
+      <c r="I41" s="10"/>
+    </row>
+    <row r="42" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C42" s="3">
         <v>35</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
-      <c r="I42" s="13"/>
-    </row>
-    <row r="43" spans="3:9">
-      <c r="C43" s="9">
+      <c r="I42" s="10"/>
+    </row>
+    <row r="43" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C43" s="3">
         <v>36</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
-      <c r="I43" s="13"/>
-    </row>
-    <row r="44" spans="3:9">
-      <c r="C44" s="9">
+      <c r="I43" s="10"/>
+    </row>
+    <row r="44" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C44" s="3">
         <v>37</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
-      <c r="I44" s="13"/>
-    </row>
-    <row r="45" spans="3:9">
-      <c r="C45" s="9">
+      <c r="I44" s="10"/>
+    </row>
+    <row r="45" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C45" s="3">
         <v>39</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
-      <c r="I45" s="13"/>
-    </row>
-    <row r="46" spans="3:9">
-      <c r="C46" s="9">
+      <c r="I45" s="10"/>
+    </row>
+    <row r="46" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C46" s="3">
         <v>40</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
-      <c r="I46" s="14"/>
-    </row>
-    <row r="47" spans="3:9">
-      <c r="I47" s="15"/>
-    </row>
-    <row r="48" spans="3:9">
-      <c r="I48" s="15"/>
-    </row>
-    <row r="49" spans="3:9">
-      <c r="I49" s="15"/>
-    </row>
-    <row r="50" spans="3:9">
+      <c r="I46" s="11"/>
+    </row>
+    <row r="50" spans="3:9" x14ac:dyDescent="0.3">
       <c r="I50">
         <f>SUM(I47:I49)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="3:9">
-      <c r="D60" s="17" t="s">
+    <row r="60" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D60" s="13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="61" spans="3:9" ht="15.75">
+    <row r="61" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="C61" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" spans="3:9">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="62" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C62" s="2">
         <v>1</v>
       </c>
-      <c r="D62" s="18" t="s">
+      <c r="D62" s="14" t="s">
         <v>5</v>
       </c>
       <c r="E62" s="5">
         <v>55640</v>
       </c>
     </row>
-    <row r="63" spans="3:9">
+    <row r="63" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C63" s="2">
         <v>2</v>
       </c>
-      <c r="D63" s="18" t="s">
+      <c r="D63" s="14" t="s">
         <v>7</v>
       </c>
       <c r="E63" s="5">
         <v>51236</v>
       </c>
     </row>
-    <row r="64" spans="3:9">
+    <row r="64" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C64" s="2">
         <v>3</v>
       </c>
-      <c r="D64" s="18" t="s">
+      <c r="D64" s="14" t="s">
         <v>21</v>
       </c>
       <c r="E64" s="5">
         <v>116407</v>
       </c>
     </row>
-    <row r="65" spans="3:5">
+    <row r="65" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C65" s="2">
         <v>4</v>
       </c>
-      <c r="D65" s="18" t="s">
+      <c r="D65" s="14" t="s">
         <v>20</v>
       </c>
       <c r="E65" s="5">
         <v>145794</v>
       </c>
     </row>
-    <row r="66" spans="3:5">
+    <row r="66" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C66" s="2">
         <v>5</v>
       </c>
-      <c r="D66" s="18" t="s">
+      <c r="D66" s="14" t="s">
         <v>13</v>
       </c>
       <c r="E66" s="5">
         <v>178457</v>
       </c>
     </row>
-    <row r="67" spans="3:5">
+    <row r="67" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C67" s="2">
         <v>6</v>
       </c>
-      <c r="D67" s="18" t="s">
+      <c r="D67" s="14" t="s">
         <v>35</v>
       </c>
       <c r="E67" s="5">
         <v>253247</v>
       </c>
     </row>
-    <row r="68" spans="3:5">
+    <row r="68" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C68" s="2">
         <v>7</v>
       </c>
-      <c r="D68" s="18" t="s">
+      <c r="D68" s="14" t="s">
         <v>14</v>
       </c>
       <c r="E68" s="5">
         <v>273321</v>
       </c>
     </row>
-    <row r="69" spans="3:5">
+    <row r="69" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C69" s="2">
         <v>8</v>
       </c>
-      <c r="D69" s="18" t="s">
+      <c r="D69" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="E69" s="12">
+      <c r="E69" s="9">
         <v>557135</v>
       </c>
     </row>
-    <row r="70" spans="3:5">
+    <row r="70" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C70" s="2">
         <v>9</v>
       </c>
-      <c r="D70" s="18" t="s">
+      <c r="D70" s="14" t="s">
         <v>30</v>
       </c>
       <c r="E70" s="5">
         <v>567205</v>
       </c>
     </row>
-    <row r="71" spans="3:5">
+    <row r="71" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C71" s="2">
         <v>10</v>
       </c>
-      <c r="D71" s="19" t="s">
+      <c r="D71" s="14" t="s">
         <v>31</v>
       </c>
       <c r="E71" s="5">
         <v>815677</v>
       </c>
     </row>
-    <row r="72" spans="3:5">
+    <row r="72" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C72" s="2">
         <v>11</v>
       </c>
-      <c r="D72" s="18" t="s">
+      <c r="D72" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E72" s="12">
+      <c r="E72" s="9">
         <v>800491</v>
       </c>
     </row>
-    <row r="73" spans="3:5">
-      <c r="C73" s="20">
+    <row r="73" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C73" s="2">
         <v>12</v>
       </c>
-      <c r="D73" s="18" t="s">
+      <c r="D73" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E73" s="12">
+      <c r="E73" s="9">
         <v>26057</v>
       </c>
     </row>
-    <row r="74" spans="3:5">
-      <c r="C74" s="20">
+    <row r="74" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C74" s="2">
         <v>13</v>
       </c>
-      <c r="D74" s="18" t="s">
+      <c r="D74" s="14" t="s">
         <v>4</v>
       </c>
       <c r="E74" s="5">
         <v>667266</v>
       </c>
     </row>
-    <row r="76" spans="3:5">
-      <c r="D76" s="21" t="s">
+    <row r="76" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="D76" s="15" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="80" spans="3:5">
+    <row r="80" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C80" s="2">
         <v>1</v>
       </c>
-      <c r="D80" s="10" t="s">
+      <c r="D80" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E80" s="11">
+      <c r="E80" s="5">
         <v>61820</v>
       </c>
     </row>
-    <row r="81" spans="3:5">
+    <row r="81" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C81" s="2">
         <v>2</v>
       </c>
-      <c r="D81" s="10" t="s">
+      <c r="D81" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E81" s="11">
+      <c r="E81" s="5">
         <v>77399</v>
       </c>
     </row>
-    <row r="82" spans="3:5">
+    <row r="82" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C82" s="2">
         <v>3</v>
       </c>
@@ -1378,7 +1390,7 @@
         <v>220637</v>
       </c>
     </row>
-    <row r="83" spans="3:5">
+    <row r="83" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C83" s="2">
         <v>4</v>
       </c>
@@ -1389,8 +1401,8 @@
         <v>173414</v>
       </c>
     </row>
-    <row r="84" spans="3:5">
-      <c r="C84" s="20">
+    <row r="84" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C84" s="2">
         <v>5</v>
       </c>
       <c r="D84" s="4" t="s">
